--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0007_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0007_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -12139,7 +12138,7 @@
         <v>0.54913531677731287</v>
       </c>
       <c r="E34" s="0">
-        <v>0.27100271002710003</v>
+        <v>0.27100271002710002</v>
       </c>
       <c r="F34" s="0">
         <v>0.017216148747525164</v>
@@ -13270,7 +13269,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="0">
-        <v>4.5277607047736082</v>
+        <v>4.5277607047736081</v>
       </c>
       <c r="U37" s="0">
         <v>0</v>
@@ -13614,7 +13613,7 @@
         <v>14.5114345114345</v>
       </c>
       <c r="N38" s="0">
-        <v>2.4922118380062282</v>
+        <v>2.4922118380062281</v>
       </c>
       <c r="O38" s="0">
         <v>0.01977456990310459</v>
@@ -14129,7 +14128,7 @@
         <v>0.40122277416889535</v>
       </c>
       <c r="BM39" s="0">
-        <v>2.1206327133669372</v>
+        <v>2.1206327133669371</v>
       </c>
       <c r="BN39" s="0">
         <v>0.62092517851598827</v>
@@ -14198,7 +14197,7 @@
         <v>0</v>
       </c>
       <c r="CJ39" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK39" s="0">
         <v>1.8305661983822885</v>
@@ -14219,7 +14218,7 @@
         <v>0.071951073270176219</v>
       </c>
       <c r="CQ39" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR39" s="0">
         <v>0</v>
@@ -14279,7 +14278,7 @@
         <v>0</v>
       </c>
       <c r="DK39" s="0">
-        <v>0.62413314840499246</v>
+        <v>0.62413314840499245</v>
       </c>
       <c r="DL39" s="0">
         <v>0</v>
@@ -14335,7 +14334,7 @@
         <v>13.585508790623322</v>
       </c>
       <c r="M40" s="0">
-        <v>4.9896049896049855</v>
+        <v>4.9896049896049854</v>
       </c>
       <c r="N40" s="0">
         <v>12.367601246105908</v>
@@ -14386,7 +14385,7 @@
         <v>1.1347517730496444</v>
       </c>
       <c r="AD40" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE40" s="0">
         <v>0</v>
@@ -14697,7 +14696,7 @@
         <v>8.524240809802917</v>
       </c>
       <c r="M41" s="0">
-        <v>1.2474012474012533</v>
+        <v>1.2474012474012532</v>
       </c>
       <c r="N41" s="0">
         <v>15.825545171339638</v>
@@ -14916,7 +14915,7 @@
         <v>0</v>
       </c>
       <c r="CH41" s="0">
-        <v>0.74201669537564941</v>
+        <v>0.7420166953756494</v>
       </c>
       <c r="CI41" s="0">
         <v>0</v>
@@ -15026,7 +15025,7 @@
         <v>14.128728414442689</v>
       </c>
       <c r="B42" s="0">
-        <v>1.8188660311088794</v>
+        <v>1.8188660311088793</v>
       </c>
       <c r="C42" s="0">
         <v>1.7322138753866534</v>
@@ -15146,7 +15145,7 @@
         <v>0.44943820224719067</v>
       </c>
       <c r="AP42" s="0">
-        <v>1.72185430463576</v>
+        <v>1.7218543046357599</v>
       </c>
       <c r="AQ42" s="0">
         <v>0.042918454935622276</v>
@@ -15185,7 +15184,7 @@
         <v>0.91661738616203348</v>
       </c>
       <c r="BC42" s="0">
-        <v>5.992889791772468</v>
+        <v>5.9928897917724679</v>
       </c>
       <c r="BD42" s="0">
         <v>13.299075025693718</v>
@@ -15314,7 +15313,7 @@
         <v>0</v>
       </c>
       <c r="CT42" s="0">
-        <v>5.4865839006808122</v>
+        <v>5.4865839006808121</v>
       </c>
       <c r="CU42" s="0">
         <v>0</v>
@@ -15418,7 +15417,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="0">
-        <v>1.5450186467767702</v>
+        <v>1.5450186467767701</v>
       </c>
       <c r="M43" s="0">
         <v>0.083160083160083095</v>
@@ -15508,7 +15507,7 @@
         <v>2.6516853932584246</v>
       </c>
       <c r="AP43" s="0">
-        <v>6.5342163355408332</v>
+        <v>6.5342163355408331</v>
       </c>
       <c r="AQ43" s="0">
         <v>0.98712446351931249</v>
@@ -15538,7 +15537,7 @@
         <v>0</v>
       </c>
       <c r="AZ43" s="0">
-        <v>4.5757688032604627</v>
+        <v>4.5757688032604626</v>
       </c>
       <c r="BA43" s="0">
         <v>5.1273985530040846</v>
@@ -15709,7 +15708,7 @@
         <v>0.20036429872495429</v>
       </c>
       <c r="DE43" s="0">
-        <v>0.1449975833736103</v>
+        <v>0.14499758337361029</v>
       </c>
       <c r="DF43" s="0">
         <v>14.008179959100191</v>
@@ -15789,7 +15788,7 @@
         <v>1.8068535825545156</v>
       </c>
       <c r="O44" s="0">
-        <v>16.33379473996439</v>
+        <v>16.333794739964389</v>
       </c>
       <c r="P44" s="0">
         <v>7.9337996928851657</v>
@@ -15891,7 +15890,7 @@
         <v>7.4893807288173422</v>
       </c>
       <c r="AW44" s="0">
-        <v>8.2077502691065583</v>
+        <v>8.2077502691065582</v>
       </c>
       <c r="AX44" s="0">
         <v>0</v>
@@ -15909,10 +15908,10 @@
         <v>7.2738024837374269</v>
       </c>
       <c r="BC44" s="0">
-        <v>13.522092432706947</v>
+        <v>13.522092432706946</v>
       </c>
       <c r="BD44" s="0">
-        <v>6.1048304213771783</v>
+        <v>6.1048304213771782</v>
       </c>
       <c r="BE44" s="0">
         <v>0</v>
@@ -16361,7 +16360,7 @@
         <v>0</v>
       </c>
       <c r="CG45" s="0">
-        <v>0.58500265910299532</v>
+        <v>0.58500265910299531</v>
       </c>
       <c r="CH45" s="0">
         <v>14.959586590698276</v>
@@ -16373,7 +16372,7 @@
         <v>15.433270082226425</v>
       </c>
       <c r="CK45" s="0">
-        <v>2.5287356321839059</v>
+        <v>2.5287356321839058</v>
       </c>
       <c r="CL45" s="0">
         <v>13.99204244031829</v>
@@ -16463,7 +16462,7 @@
         <v>8.3984374999999929</v>
       </c>
       <c r="DO45" s="0">
-        <v>0.97087378640776601</v>
+        <v>0.970873786407766</v>
       </c>
       <c r="DP45" s="0">
         <v>0.70422535211267545</v>
@@ -16666,7 +16665,7 @@
         <v>0.50408482530853427</v>
       </c>
       <c r="BN46" s="0">
-        <v>1.6764979819931683</v>
+        <v>1.6764979819931682</v>
       </c>
       <c r="BO46" s="0">
         <v>0.033772374197906088</v>
@@ -16920,7 +16919,7 @@
         <v>0.78014184397163489</v>
       </c>
       <c r="AD47" s="0">
-        <v>6.5667380442541346</v>
+        <v>6.5667380442541345</v>
       </c>
       <c r="AE47" s="0">
         <v>14.549180327868919</v>
@@ -16959,7 +16958,7 @@
         <v>6.4459161147903172</v>
       </c>
       <c r="AQ47" s="0">
-        <v>14.420600858369165</v>
+        <v>14.420600858369164</v>
       </c>
       <c r="AR47" s="0">
         <v>0.93457943925234077</v>
@@ -17058,7 +17057,7 @@
         <v>15.043859649122878</v>
       </c>
       <c r="BX47" s="0">
-        <v>1.3462347496844827</v>
+        <v>1.3462347496844826</v>
       </c>
       <c r="BY47" s="0">
         <v>0.75250836120401687</v>
@@ -17070,7 +17069,7 @@
         <v>0</v>
       </c>
       <c r="CB47" s="0">
-        <v>9.2913385826772093</v>
+        <v>9.2913385826772092</v>
       </c>
       <c r="CC47" s="0">
         <v>5.6617922759655306</v>
@@ -17139,7 +17138,7 @@
         <v>7.4784276126558362</v>
       </c>
       <c r="CY47" s="0">
-        <v>2.1638706540238371</v>
+        <v>2.163870654023837</v>
       </c>
       <c r="CZ47" s="0">
         <v>7.2011186203682467</v>
@@ -17357,13 +17356,13 @@
         <v>4.5535186280307469</v>
       </c>
       <c r="BC48" s="0">
-        <v>0.50787201625190404</v>
+        <v>0.50787201625190403</v>
       </c>
       <c r="BD48" s="0">
-        <v>0.020554984583761545</v>
+        <v>0.020554984583761544</v>
       </c>
       <c r="BE48" s="0">
-        <v>8.766994842944202</v>
+        <v>8.7669948429442019</v>
       </c>
       <c r="BF48" s="0">
         <v>2.1657642648896274</v>
@@ -17408,7 +17407,7 @@
         <v>9.5601599418393235</v>
       </c>
       <c r="BT48" s="0">
-        <v>4.1083693716611514</v>
+        <v>4.1083693716611513</v>
       </c>
       <c r="BU48" s="0">
         <v>2.8287224121852632</v>
@@ -17420,7 +17419,7 @@
         <v>9.6052631578947274</v>
       </c>
       <c r="BX48" s="0">
-        <v>0.33655868742111878</v>
+        <v>0.33655868742111877</v>
       </c>
       <c r="BY48" s="0">
         <v>0.16722408026755839</v>
@@ -17444,7 +17443,7 @@
         <v>16.952380952380938</v>
       </c>
       <c r="CF48" s="0">
-        <v>2.2452504317789273</v>
+        <v>2.2452504317789272</v>
       </c>
       <c r="CG48" s="0">
         <v>12.090054954795237</v>
@@ -17710,7 +17709,7 @@
         <v>13.811931243680474</v>
       </c>
       <c r="AZ49" s="0">
-        <v>0.51871063356798775</v>
+        <v>0.51871063356798774</v>
       </c>
       <c r="BA49" s="0">
         <v>0.72349795533186478</v>
@@ -17803,7 +17802,7 @@
         <v>6.6538461538461471</v>
       </c>
       <c r="CE49" s="0">
-        <v>18.857142857142844</v>
+        <v>18.857142857142843</v>
       </c>
       <c r="CF49" s="0">
         <v>6.2176165803108754</v>
@@ -17830,7 +17829,7 @@
         <v>7.6579094466182154</v>
       </c>
       <c r="CN49" s="0">
-        <v>5.8147882268485232</v>
+        <v>5.8147882268485231</v>
       </c>
       <c r="CO49" s="0">
         <v>0.27770431102882809</v>
@@ -18051,7 +18050,7 @@
         <v>13.86915887850466</v>
       </c>
       <c r="AS50" s="0">
-        <v>17.857142857142844</v>
+        <v>17.857142857142843</v>
       </c>
       <c r="AT50" s="0">
         <v>17.028380634390636</v>
@@ -18093,7 +18092,7 @@
         <v>12.244897959183662</v>
       </c>
       <c r="BG50" s="0">
-        <v>11.700554528650637</v>
+        <v>11.700554528650636</v>
       </c>
       <c r="BH50" s="0">
         <v>8.0321285140562182</v>
@@ -18180,7 +18179,7 @@
         <v>1.0648918469217961</v>
       </c>
       <c r="CJ50" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK50" s="0">
         <v>0</v>
@@ -18207,7 +18206,7 @@
         <v>5.273250239693188</v>
       </c>
       <c r="CS50" s="0">
-        <v>4.7987616099071167</v>
+        <v>4.7987616099071166</v>
       </c>
       <c r="CT50" s="0">
         <v>0</v>
@@ -18548,7 +18547,7 @@
         <v>0</v>
       </c>
       <c r="CL51" s="0">
-        <v>0.047366426676771462</v>
+        <v>0.047366426676771461</v>
       </c>
       <c r="CM51" s="0">
         <v>0.33538289547233063</v>
@@ -18892,7 +18891,7 @@
         <v>0.57142857142857095</v>
       </c>
       <c r="CF52" s="0">
-        <v>17.098445595854909</v>
+        <v>17.098445595854908</v>
       </c>
       <c r="CG52" s="0">
         <v>1.8259173905335919</v>
@@ -18955,7 +18954,7 @@
         <v>0</v>
       </c>
       <c r="DA52" s="0">
-        <v>20.74927953890488</v>
+        <v>20.749279538904879</v>
       </c>
       <c r="DB52" s="0">
         <v>10.815047021943563</v>
@@ -18964,7 +18963,7 @@
         <v>1.9757521329142327</v>
       </c>
       <c r="DD52" s="0">
-        <v>0.12750455373406181</v>
+        <v>0.1275045537340618</v>
       </c>
       <c r="DE52" s="0">
         <v>0.24166263895601717</v>
@@ -19071,7 +19070,7 @@
         <v>0</v>
       </c>
       <c r="W53" s="0">
-        <v>6.5641025641025586</v>
+        <v>6.5641025641025585</v>
       </c>
       <c r="X53" s="0">
         <v>0</v>
@@ -19095,7 +19094,7 @@
         <v>0</v>
       </c>
       <c r="AE53" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF53" s="0">
         <v>0.42105263157894701</v>
@@ -19278,7 +19277,7 @@
         <v>0</v>
       </c>
       <c r="CN53" s="0">
-        <v>5.7430007178750842</v>
+        <v>5.7430007178750841</v>
       </c>
       <c r="CO53" s="0">
         <v>0</v>
@@ -19293,7 +19292,7 @@
         <v>0.015979546180888447</v>
       </c>
       <c r="CS53" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT53" s="0">
         <v>0</v>
@@ -19433,7 +19432,7 @@
         <v>0</v>
       </c>
       <c r="W54" s="0">
-        <v>2.9230769230769203</v>
+        <v>2.9230769230769202</v>
       </c>
       <c r="X54" s="0">
         <v>0</v>
@@ -19550,7 +19549,7 @@
         <v>1.6783216783216768</v>
       </c>
       <c r="BJ54" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK54" s="0">
         <v>0</v>
@@ -19661,7 +19660,7 @@
         <v>0</v>
       </c>
       <c r="CU54" s="0">
-        <v>20.359281437125731</v>
+        <v>20.35928143712573</v>
       </c>
       <c r="CV54" s="0">
         <v>17.910447761194014</v>
@@ -19978,7 +19977,7 @@
         <v>0</v>
       </c>
       <c r="CF55" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG55" s="0">
         <v>0</v>
@@ -24139,7 +24138,7 @@
         <v>0</v>
       </c>
       <c r="W67" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X67" s="0">
         <v>0</v>
@@ -24501,7 +24500,7 @@
         <v>0</v>
       </c>
       <c r="W68" s="0">
-        <v>0.66666666666666608</v>
+        <v>0.66666666666666607</v>
       </c>
       <c r="X68" s="0">
         <v>0</v>
@@ -24564,7 +24563,7 @@
         <v>0</v>
       </c>
       <c r="AR68" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS68" s="0">
         <v>0</v>
@@ -24618,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="BJ68" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK68" s="0">
         <v>0</v>
@@ -24759,7 +24758,7 @@
         <v>0</v>
       </c>
       <c r="DE68" s="0">
-        <v>0.096665055582406873</v>
+        <v>0.096665055582406872</v>
       </c>
       <c r="DF68" s="0">
         <v>0</v>
@@ -25309,7 +25308,7 @@
         <v>0.0303859009419629</v>
       </c>
       <c r="AY70" s="0">
-        <v>0.3640040444893829</v>
+        <v>0.36400404448938289</v>
       </c>
       <c r="AZ70" s="0">
         <v>0</v>
@@ -25411,7 +25410,7 @@
         <v>0</v>
       </c>
       <c r="CG70" s="0">
-        <v>1.1877326715121424</v>
+        <v>1.1877326715121423</v>
       </c>
       <c r="CH70" s="0">
         <v>0</v>
@@ -25447,7 +25446,7 @@
         <v>0.99073186321508389</v>
       </c>
       <c r="CS70" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT70" s="0">
         <v>0</v>
@@ -25809,7 +25808,7 @@
         <v>3.243847874720355</v>
       </c>
       <c r="CS71" s="0">
-        <v>0.13268465280849171</v>
+        <v>0.1326846528084917</v>
       </c>
       <c r="CT71" s="0">
         <v>0</v>
@@ -26566,7 +26565,7 @@
         <v>0.022451728783116277</v>
       </c>
       <c r="DD73" s="0">
-        <v>0.12750455373406181</v>
+        <v>0.1275045537340618</v>
       </c>
       <c r="DE73" s="0">
         <v>12.566457225712893</v>
@@ -27170,7 +27169,7 @@
         <v>0</v>
       </c>
       <c r="BP75" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ75" s="0">
         <v>0.68198133524766635</v>
@@ -27622,7 +27621,7 @@
         <v>11.698363555948685</v>
       </c>
       <c r="CT76" s="0">
-        <v>0.46055266319583455</v>
+        <v>0.46055266319583454</v>
       </c>
       <c r="CU76" s="0">
         <v>0.59880239520958034</v>
@@ -27804,7 +27803,7 @@
         <v>0.066859817249832795</v>
       </c>
       <c r="AL77" s="0">
-        <v>3.0179918746372581</v>
+        <v>3.017991874637258</v>
       </c>
       <c r="AM77" s="0">
         <v>11.306765523632983</v>
@@ -27897,7 +27896,7 @@
         <v>0.61728395061728336</v>
       </c>
       <c r="BQ77" s="0">
-        <v>7.7171572146446446</v>
+        <v>7.7171572146446445</v>
       </c>
       <c r="BR77" s="0">
         <v>1.816420440784692</v>
@@ -27981,7 +27980,7 @@
         <v>1.1185682326621915</v>
       </c>
       <c r="CS77" s="0">
-        <v>6.7448031844316621</v>
+        <v>6.744803184431662</v>
       </c>
       <c r="CT77" s="0">
         <v>2.0424509411293532</v>
@@ -28011,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="DC77" s="0">
-        <v>4.8944768747193495</v>
+        <v>4.8944768747193494</v>
       </c>
       <c r="DD77" s="0">
         <v>10.965391621129317</v>
@@ -28041,7 +28040,7 @@
         <v>0</v>
       </c>
       <c r="DM77" s="0">
-        <v>6.1965811965811915</v>
+        <v>6.1965811965811914</v>
       </c>
       <c r="DN77" s="0">
         <v>0</v>
@@ -28235,7 +28234,7 @@
         <v>3.9993306559571584</v>
       </c>
       <c r="BI78" s="0">
-        <v>7.7783754706831561</v>
+        <v>7.778375470683156</v>
       </c>
       <c r="BJ78" s="0">
         <v>0.13266998341625194</v>
@@ -28304,7 +28303,7 @@
         <v>0</v>
       </c>
       <c r="CF78" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG78" s="0">
         <v>0.10636411983690826</v>
@@ -28316,13 +28315,13 @@
         <v>0.83194675540765317</v>
       </c>
       <c r="CJ78" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK78" s="0">
         <v>0.0085142613878245992</v>
       </c>
       <c r="CL78" s="0">
-        <v>0.96627510420613783</v>
+        <v>0.96627510420613782</v>
       </c>
       <c r="CM78" s="0">
         <v>9.8378982671883648</v>
@@ -28726,7 +28725,7 @@
         <v>12.13226355458302</v>
       </c>
       <c r="CZ79" s="0">
-        <v>5.8727569331158192</v>
+        <v>5.8727569331158191</v>
       </c>
       <c r="DA79" s="0">
         <v>0</v>
@@ -28738,7 +28737,7 @@
         <v>9.8787606645711641</v>
       </c>
       <c r="DD79" s="0">
-        <v>7.1584699453551846</v>
+        <v>7.1584699453551845</v>
       </c>
       <c r="DE79" s="0">
         <v>0</v>
@@ -28782,7 +28781,7 @@
         <v>0</v>
       </c>
       <c r="B80" s="0">
-        <v>0.18815855494229789</v>
+        <v>0.18815855494229788</v>
       </c>
       <c r="C80" s="0">
         <v>0.23862129916040631</v>
@@ -28848,7 +28847,7 @@
         <v>0</v>
       </c>
       <c r="X80" s="0">
-        <v>5.8555997725980618</v>
+        <v>5.8555997725980617</v>
       </c>
       <c r="Y80" s="0">
         <v>3.8522012578616316</v>
@@ -28932,7 +28931,7 @@
         <v>0</v>
       </c>
       <c r="AZ80" s="0">
-        <v>1.9266394961096685</v>
+        <v>1.9266394961096684</v>
       </c>
       <c r="BA80" s="0">
         <v>6.2598301352626562</v>
@@ -28965,7 +28964,7 @@
         <v>0</v>
       </c>
       <c r="BK80" s="0">
-        <v>1.0508963527714808</v>
+        <v>1.0508963527714807</v>
       </c>
       <c r="BL80" s="0">
         <v>8.5212074894917773</v>
@@ -29022,7 +29021,7 @@
         <v>1.1248593925759269</v>
       </c>
       <c r="CD80" s="0">
-        <v>9.5384615384615295</v>
+        <v>9.5384615384615294</v>
       </c>
       <c r="CE80" s="0">
         <v>0</v>
@@ -29067,7 +29066,7 @@
         <v>0</v>
       </c>
       <c r="CS80" s="0">
-        <v>0.13268465280849171</v>
+        <v>0.1326846528084917</v>
       </c>
       <c r="CT80" s="0">
         <v>12.474969963956738</v>
@@ -29156,10 +29155,10 @@
         <v>0.98121670871881039</v>
       </c>
       <c r="F81" s="0">
-        <v>3.5293104932426585</v>
+        <v>3.5293104932426584</v>
       </c>
       <c r="G81" s="0">
-        <v>0.80128205128205055</v>
+        <v>0.80128205128205054</v>
       </c>
       <c r="H81" s="0">
         <v>0</v>
@@ -29396,13 +29395,13 @@
         <v>0</v>
       </c>
       <c r="CH81" s="0">
-        <v>3.2728236385318637</v>
+        <v>3.2728236385318636</v>
       </c>
       <c r="CI81" s="0">
         <v>10.648918469217961</v>
       </c>
       <c r="CJ81" s="0">
-        <v>1.5496521189120796</v>
+        <v>1.5496521189120795</v>
       </c>
       <c r="CK81" s="0">
         <v>2.8011919965942931</v>
@@ -29417,7 +29416,7 @@
         <v>0</v>
       </c>
       <c r="CO81" s="0">
-        <v>0.13224014810896576</v>
+        <v>0.13224014810896575</v>
       </c>
       <c r="CP81" s="0">
         <v>0</v>
@@ -29429,7 +29428,7 @@
         <v>0</v>
       </c>
       <c r="CS81" s="0">
-        <v>0.044228217602830571</v>
+        <v>0.04422821760283057</v>
       </c>
       <c r="CT81" s="0">
         <v>9.0909090909090828</v>
@@ -29734,7 +29733,7 @@
         <v>1.2123745819398117</v>
       </c>
       <c r="BZ82" s="0">
-        <v>1.3033175355450371</v>
+        <v>1.303317535545037</v>
       </c>
       <c r="CA82" s="0">
         <v>2.8571428571428861</v>
@@ -29857,7 +29856,7 @@
         <v>7.4218750000000755</v>
       </c>
       <c r="DO82" s="0">
-        <v>1.9417475728155536</v>
+        <v>1.9417475728155535</v>
       </c>
       <c r="DP82" s="0">
         <v>0</v>
@@ -29883,7 +29882,7 @@
         <v>11.715589222690873</v>
       </c>
       <c r="G83" s="0">
-        <v>9.094551282051274</v>
+        <v>9.0945512820512739</v>
       </c>
       <c r="H83" s="0">
         <v>0</v>
@@ -30452,7 +30451,7 @@
         <v>10.526315789473674</v>
       </c>
       <c r="BX84" s="0">
-        <v>0.33655868742111878</v>
+        <v>0.33655868742111877</v>
       </c>
       <c r="BY84" s="0">
         <v>8.1103678929765817</v>
@@ -30470,7 +30469,7 @@
         <v>0.037495313085864235</v>
       </c>
       <c r="CD84" s="0">
-        <v>0.88461538461538381</v>
+        <v>0.8846153846153838</v>
       </c>
       <c r="CE84" s="0">
         <v>0</v>
@@ -30533,7 +30532,7 @@
         <v>2.3489932885906022</v>
       </c>
       <c r="CY84" s="0">
-        <v>0.048626306831996064</v>
+        <v>0.048626306831996063</v>
       </c>
       <c r="CZ84" s="0">
         <v>0</v>
@@ -30781,7 +30780,7 @@
         <v>0</v>
       </c>
       <c r="BM85" s="0">
-        <v>0.15644011819920029</v>
+        <v>0.15644011819920028</v>
       </c>
       <c r="BN85" s="0">
         <v>0.062092517851598826</v>
@@ -30853,7 +30852,7 @@
         <v>7.5268817204301008</v>
       </c>
       <c r="CK85" s="0">
-        <v>8.0119199659429477</v>
+        <v>8.0119199659429476</v>
       </c>
       <c r="CL85" s="0">
         <v>0.6915498294808633</v>
@@ -30868,7 +30867,7 @@
         <v>0</v>
       </c>
       <c r="CP85" s="0">
-        <v>0.26382060199064617</v>
+        <v>0.26382060199064616</v>
       </c>
       <c r="CQ85" s="0">
         <v>0</v>
@@ -30957,7 +30956,7 @@
         <v>7.1374811841444998</v>
       </c>
       <c r="C86" s="0">
-        <v>7.2293415819708296</v>
+        <v>7.2293415819708295</v>
       </c>
       <c r="D86" s="0">
         <v>5.3274321776903486</v>
@@ -30972,7 +30971,7 @@
         <v>7.4118589743589682</v>
       </c>
       <c r="H86" s="0">
-        <v>1.9981834695731136</v>
+        <v>1.9981834695731135</v>
       </c>
       <c r="I86" s="0">
         <v>8.6877076411960061</v>
@@ -31331,7 +31330,7 @@
         <v>0.68003787552724393</v>
       </c>
       <c r="G87" s="0">
-        <v>2.644230769230767</v>
+        <v>2.6442307692307669</v>
       </c>
       <c r="H87" s="0">
         <v>4.9046321525885519</v>
@@ -31577,7 +31576,7 @@
         <v>1.2650221378874118</v>
       </c>
       <c r="CK87" s="0">
-        <v>0.84291187739463525</v>
+        <v>0.84291187739463524</v>
       </c>
       <c r="CL87" s="0">
         <v>0.0094732853353542926</v>
@@ -31664,7 +31663,7 @@
         <v>0</v>
       </c>
       <c r="DN87" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO87" s="0">
         <v>3.15533980582524</v>
@@ -31708,7 +31707,7 @@
         <v>0.39908779931584915</v>
       </c>
       <c r="L88" s="0">
-        <v>1.1188066062866267</v>
+        <v>1.1188066062866266</v>
       </c>
       <c r="M88" s="0">
         <v>3.2432432432432408</v>
@@ -31729,7 +31728,7 @@
         <v>0</v>
       </c>
       <c r="S88" s="0">
-        <v>5.9626636946224521</v>
+        <v>5.962663694622452</v>
       </c>
       <c r="T88" s="0">
         <v>4.2819094447859003</v>
@@ -31921,7 +31920,7 @@
         <v>0</v>
       </c>
       <c r="CE88" s="0">
-        <v>6.6666666666666608</v>
+        <v>6.6666666666666607</v>
       </c>
       <c r="CF88" s="0">
         <v>0</v>
@@ -32032,7 +32031,7 @@
         <v>0.485436893203883</v>
       </c>
       <c r="DP88" s="0">
-        <v>7.3943661971830919</v>
+        <v>7.3943661971830918</v>
       </c>
     </row>
     <row r="89">
@@ -32049,7 +32048,7 @@
         <v>0.065568396033111986</v>
       </c>
       <c r="E89" s="0">
-        <v>0.24296794692084831</v>
+        <v>0.2429679469208483</v>
       </c>
       <c r="F89" s="0">
         <v>0.025824223121287744</v>
@@ -32259,7 +32258,7 @@
         <v>0</v>
       </c>
       <c r="BW89" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX89" s="0">
         <v>9.1712242322254856</v>
@@ -32301,7 +32300,7 @@
         <v>0.094876660341555896</v>
       </c>
       <c r="CK89" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL89" s="0">
         <v>0</v>
@@ -32815,7 +32814,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="0">
-        <v>5.4193368626358272</v>
+        <v>5.4193368626358271</v>
       </c>
       <c r="T91" s="0">
         <v>0.061462814996926803</v>
@@ -33007,7 +33006,7 @@
         <v>0</v>
       </c>
       <c r="CE91" s="0">
-        <v>3.8095238095238067</v>
+        <v>3.8095238095238066</v>
       </c>
       <c r="CF91" s="0">
         <v>0</v>
@@ -33764,7 +33763,7 @@
         <v>0</v>
       </c>
       <c r="CP93" s="0">
-        <v>0.38373905744093984</v>
+        <v>0.38373905744093983</v>
       </c>
       <c r="CQ93" s="0">
         <v>0</v>
